--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.36853788320485</v>
+        <v>2.172387406020789</v>
       </c>
       <c r="D2" t="n">
-        <v>13.29858454628513</v>
+        <v>2.161019988771333</v>
       </c>
       <c r="E2" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F2" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.49888203413441</v>
+        <v>8.206068330546842</v>
       </c>
       <c r="D3" t="n">
-        <v>44.50848967190298</v>
+        <v>7.232629571684234</v>
       </c>
       <c r="E3" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F3" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.28002478313795</v>
+        <v>5.245504027259916</v>
       </c>
       <c r="D4" t="n">
-        <v>27.01533129539595</v>
+        <v>4.389991335501843</v>
       </c>
       <c r="E4" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.20768647468107</v>
+        <v>9.296249052135673</v>
       </c>
       <c r="D5" t="n">
-        <v>48.70831551183021</v>
+        <v>7.91510127067241</v>
       </c>
       <c r="E5" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F5" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.53356527421443</v>
+        <v>5.449204357059846</v>
       </c>
       <c r="D6" t="n">
-        <v>39.49307692494977</v>
+        <v>6.417625000304338</v>
       </c>
       <c r="E6" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F6" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.33963466951955</v>
+        <v>3.142690633796927</v>
       </c>
       <c r="D7" t="n">
-        <v>18.02179067068722</v>
+        <v>2.928540983986673</v>
       </c>
       <c r="E7" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F7" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.866058887729679</v>
+        <v>0.6282345692560728</v>
       </c>
       <c r="D8" t="n">
-        <v>3.685777500247666</v>
+        <v>0.5989388437902458</v>
       </c>
       <c r="E8" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F8" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.67906195429979</v>
+        <v>3.685347567573716</v>
       </c>
       <c r="D9" t="n">
-        <v>22.37921866757719</v>
+        <v>3.636623033481294</v>
       </c>
       <c r="E9" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F9" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>75.86222859394101</v>
+        <v>12.32761214651542</v>
       </c>
       <c r="D10" t="n">
-        <v>47.05581791872287</v>
+        <v>7.646570411792466</v>
       </c>
       <c r="E10" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F10" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>56.58765901582299</v>
+        <v>9.195494590071236</v>
       </c>
       <c r="D11" t="n">
-        <v>44.54396748228092</v>
+        <v>7.238394715870649</v>
       </c>
       <c r="E11" t="n">
-        <v>21.65597866325217</v>
+        <v>3.519096532778477</v>
       </c>
       <c r="F11" t="n">
-        <v>15.25547229529278</v>
+        <v>2.479014247985076</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
